--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N65_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N65_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.96220823810837</v>
+        <v>2.59385883869261</v>
       </c>
       <c r="D2" t="n">
-        <v>23.02652086758454</v>
+        <v>3.741809640982488</v>
       </c>
       <c r="E2" t="n">
-        <v>14.723386756006</v>
+        <v>2.392550347850976</v>
       </c>
       <c r="F2" t="n">
-        <v>6.330634656556708</v>
+        <v>1.028728131690465</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.40898175012038</v>
+        <v>7.378959534394562</v>
       </c>
       <c r="D3" t="n">
-        <v>10.36525155447112</v>
+        <v>1.684353377601558</v>
       </c>
       <c r="E3" t="n">
-        <v>14.723386756006</v>
+        <v>2.392550347850976</v>
       </c>
       <c r="F3" t="n">
-        <v>6.330634656556708</v>
+        <v>1.028728131690465</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
